--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-09-29 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24.66</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>21.95</v>
+        <v>219.52</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21.85</v>
+        <v>218.48</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>21.17</v>
+        <v>211.72</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.61</v>
+        <v>206.05</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.36</v>
+        <v>203.61</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.04</v>
+        <v>150.35</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.76</v>
+        <v>107.65</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10.22</v>
+        <v>102.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:03</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:01</t>
+    <t xml:space="preserve">2026-10-05 07:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
